--- a/data/commands.xlsx
+++ b/data/commands.xlsx
@@ -21,7 +21,7 @@
     <t>Get-Process</t>
   </si>
   <si>
-    <t>gnome-keyring-daemon</t>
+    <t>playwright</t>
   </si>
   <si>
     <t>pwd</t>

--- a/data/commands.xlsx
+++ b/data/commands.xlsx
@@ -3,10 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -16,38 +18,96 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>Get-Process</t>
-  </si>
-  <si>
-    <t>playwright</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Command</t>
+  </si>
+  <si>
+    <t>Expected</t>
+  </si>
+  <si>
+    <t>CheckType</t>
+  </si>
+  <si>
+    <t>powershell</t>
+  </si>
+  <si>
+    <t>Get-Date</t>
+  </si>
+  <si>
+    <t>contains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">echo Hello</t>
+  </si>
+  <si>
+    <t>Hello</t>
+  </si>
+  <si>
+    <t>equals</t>
   </si>
   <si>
     <t>pwd</t>
   </si>
   <si>
     <t>home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get-ChildItem -Recurse | Out-String</t>
+  </si>
+  <si>
+    <t>wkWorkers.js</t>
+  </si>
+  <si>
+    <t xml:space="preserve">echo Step1</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">echo Step2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">echo Step3</t>
+  </si>
+  <si>
+    <t>Step2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11.000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="5"/>
+        <bgColor indexed="5"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -62,7 +122,13 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
@@ -566,24 +632,60 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.57421875"/>
-    <col customWidth="1" min="2" max="2" width="23.28125"/>
+    <col customWidth="1" min="1" max="1" width="43.140625"/>
+    <col customWidth="1" min="2" max="2" width="33.00390625"/>
+    <col customWidth="1" min="3" max="3" width="24.140625"/>
+    <col customWidth="1" min="4" max="4" width="23.00390625"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" ht="14.25">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -592,4 +694,131 @@
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="0" copies="1"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="33.421875"/>
+    <col customWidth="1" min="3" max="3" width="38.00390625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="43.140625"/>
+    <col customWidth="1" min="2" max="2" width="33.00390625"/>
+    <col customWidth="1" min="3" max="3" width="24.140625"/>
+    <col customWidth="1" min="4" max="4" width="23.00390625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/data/commands.xlsx
+++ b/data/commands.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -18,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Action</t>
   </si>
@@ -75,6 +76,18 @@
   </si>
   <si>
     <t>Step2</t>
+  </si>
+  <si>
+    <t>sql</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT COUNT(*) as cnt FROM users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT [user] FROM users WHERE id=1</t>
+  </si>
+  <si>
+    <t>alice</t>
   </si>
 </sst>
 </file>
@@ -122,14 +135,13 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -698,7 +710,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="33.421875"/>
     <col customWidth="1" min="3" max="3" width="38.00390625"/>
@@ -739,7 +751,7 @@
       <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" t="s">
@@ -808,10 +820,84 @@
       <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="43.140625"/>
+    <col customWidth="1" min="2" max="2" width="46.7109375"/>
+    <col customWidth="1" min="3" max="3" width="24.140625"/>
+    <col customWidth="1" min="4" max="4" width="23.00390625"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25">
+      <c r="A3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25">
+      <c r="A4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>6</v>
       </c>
     </row>

--- a/data/commands.xlsx
+++ b/data/commands.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Action</t>
   </si>
@@ -75,7 +75,7 @@
     <t xml:space="preserve">echo Step3</t>
   </si>
   <si>
-    <t>Step2</t>
+    <t>Step3</t>
   </si>
   <si>
     <t>sql</t>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>alice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">echo ${port}</t>
   </si>
 </sst>
 </file>
@@ -820,7 +823,7 @@
       <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D4" t="s">
@@ -863,42 +866,64 @@
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="3">
         <v>2026</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5">
+        <v>1433</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/data/commands.xlsx
+++ b/data/commands.xlsx
@@ -912,7 +912,7 @@
         <v>23</v>
       </c>
       <c r="C5">
-        <v>1433</v>
+        <v>1544</v>
       </c>
       <c r="D5" t="s">
         <v>9</v>

--- a/data/commands.xlsx
+++ b/data/commands.xlsx
@@ -3,13 +3,10 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -19,18 +16,66 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Command</t>
-  </si>
-  <si>
-    <t>Expected</t>
-  </si>
-  <si>
-    <t>CheckType</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+  <si>
+    <t>ACTION</t>
+  </si>
+  <si>
+    <t>COMMAND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALUE 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALUE 2</t>
+  </si>
+  <si>
+    <t>EXPECTED</t>
+  </si>
+  <si>
+    <t>CHECK</t>
+  </si>
+  <si>
+    <t>web</t>
+  </si>
+  <si>
+    <t>openPage</t>
+  </si>
+  <si>
+    <t>https://www.saucedemo.com</t>
+  </si>
+  <si>
+    <t>webGetUrl</t>
+  </si>
+  <si>
+    <t>inputText</t>
+  </si>
+  <si>
+    <t>#user-name</t>
+  </si>
+  <si>
+    <t>standard_user</t>
+  </si>
+  <si>
+    <t>#password</t>
+  </si>
+  <si>
+    <t>secret_sauce</t>
+  </si>
+  <si>
+    <t>clickButton</t>
+  </si>
+  <si>
+    <t>#login-button</t>
+  </si>
+  <si>
+    <t>webElementVisible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">//*[@class="title" and text()="Products"]</t>
+  </si>
+  <si>
+    <t>https://www.saucedemo.com/inventory.html/</t>
   </si>
   <si>
     <t>powershell</t>
@@ -49,55 +94,13 @@
   </si>
   <si>
     <t>equals</t>
-  </si>
-  <si>
-    <t>pwd</t>
-  </si>
-  <si>
-    <t>home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Get-ChildItem -Recurse | Out-String</t>
-  </si>
-  <si>
-    <t>wkWorkers.js</t>
-  </si>
-  <si>
-    <t xml:space="preserve">echo Step1</t>
-  </si>
-  <si>
-    <t>Step</t>
-  </si>
-  <si>
-    <t xml:space="preserve">echo Step2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">echo Step3</t>
-  </si>
-  <si>
-    <t>Step3</t>
-  </si>
-  <si>
-    <t>sql</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELECT COUNT(*) as cnt FROM users</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELECT [user] FROM users WHERE id=1</t>
-  </si>
-  <si>
-    <t>alice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">echo ${port}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -111,6 +114,12 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11.000000"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -121,12 +130,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="5"/>
-        <bgColor indexed="5"/>
+        <fgColor indexed="26"/>
+        <bgColor indexed="26"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -134,23 +143,39 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" applyNumberFormat="0" applyFont="0" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="1" builtinId="10"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -649,8 +674,10 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="43.140625"/>
     <col customWidth="1" min="2" max="2" width="33.00390625"/>
-    <col customWidth="1" min="3" max="3" width="24.140625"/>
-    <col customWidth="1" min="4" max="4" width="23.00390625"/>
+    <col customWidth="1" min="3" max="3" width="45.28125"/>
+    <col customWidth="1" min="4" max="4" width="45.8515625"/>
+    <col customWidth="1" min="5" max="5" width="24.140625"/>
+    <col customWidth="1" min="6" max="6" width="23.00390625"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
@@ -666,270 +693,143 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" ht="14.25">
       <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2"/>
+      <c r="F2" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" ht="14.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2026</v>
-      </c>
-      <c r="D3" t="s">
         <v>6</v>
       </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" ht="14.25">
       <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5"/>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6"/>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>9</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7"/>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="7">
+        <v>2026</v>
+      </c>
+      <c r="F8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="C2"/>
+    <hyperlink r:id="rId2" ref="C7"/>
+  </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="0" copies="1"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col customWidth="1" min="2" max="2" width="33.421875"/>
-    <col customWidth="1" min="3" max="3" width="38.00390625"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="43.140625"/>
-    <col customWidth="1" min="2" max="2" width="33.00390625"/>
-    <col customWidth="1" min="3" max="3" width="24.140625"/>
-    <col customWidth="1" min="4" max="4" width="23.00390625"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="3"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="43.140625"/>
-    <col customWidth="1" min="2" max="2" width="46.7109375"/>
-    <col customWidth="1" min="3" max="3" width="24.140625"/>
-    <col customWidth="1" min="4" max="4" width="23.00390625"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="14.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" ht="14.25">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25">
-      <c r="A3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25">
-      <c r="A4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5">
-        <v>1544</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25">
-      <c r="A6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
 </file>